--- a/stock.xlsx
+++ b/stock.xlsx
@@ -507,17 +507,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>76,100</t>
+          <t>77,300</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-900</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4,543,005</t>
+          <t>4,614,642</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,17 +537,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>51.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12,877,239</t>
+          <t>11,846,941</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -577,12 +577,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3,500</t>
+          <t>-1,500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.26%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3,584,461</t>
+          <t>2,184,456</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -637,17 +637,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>402,000</t>
+          <t>405,500</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+1,500</t>
+          <t>+5,500</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>660,339</t>
+          <t>666,088</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>613,433</t>
+          <t>572,573</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>916,000</t>
+          <t>922,000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>+2,000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>606,071</t>
+          <t>610,041</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>55,610</t>
+          <t>46,551</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>181.03</t>
+          <t>182.21</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>71,500</t>
+          <t>71,700</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-300</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>588,364</t>
+          <t>590,010</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.28</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1,009,997</t>
+          <t>1,049,103</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -822,62 +822,62 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>121,500</t>
+          <t>761,000</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>+1,000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>540,665</t>
+          <t>537,208</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>444,992</t>
+          <t>70,592</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4,738,694</t>
+          <t>398,670</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>113.23</t>
+          <t>20.50</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.93</t>
         </is>
       </c>
     </row>
@@ -887,62 +887,62 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>716,000</t>
+          <t>119,500</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>+4,500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+3.91%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>505,441</t>
+          <t>531,766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70,592</t>
+          <t>444,992</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>246,473</t>
+          <t>5,290,884</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>111.37</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
@@ -962,17 +962,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>725,000</t>
+          <t>726,000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-25,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>498,543</t>
+          <t>499,230</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>44.90</t>
+          <t>44.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>719,298</t>
+          <t>163,704</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>53.72</t>
+          <t>53.79</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>208,000</t>
+          <t>207,000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>444,430</t>
+          <t>442,293</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>413,002</t>
+          <t>409,939</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>267,000</t>
+          <t>274,500</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-5,500</t>
+          <t>-10,000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>368,286</t>
+          <t>378,631</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1122,17 +1122,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>350,283</t>
+          <t>623,545</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>62.60</t>
+          <t>64.36</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>84,500</t>
+          <t>82,600</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+1,200</t>
+          <t>-1,600</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>342,532</t>
+          <t>334,830</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1187,17 +1187,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1,420,680</t>
+          <t>1,168,511</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>67,100</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-1,900</t>
+          <t>+2,600</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>318,792</t>
+          <t>327,819</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2,413,749</t>
+          <t>2,107,645</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>217.15</t>
+          <t>223.30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>364,500</t>
+          <t>345,000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+3,000</t>
+          <t>-1,500</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>317,796</t>
+          <t>300,795</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>55.24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>257,845</t>
+          <t>472,423</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>270,500</t>
+          <t>260,000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+1,500</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>256,415</t>
+          <t>246,462</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1382,17 +1382,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>193,944</t>
+          <t>249,174</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11.61</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1417,17 +1417,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>492,000</t>
+          <t>493,000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-1,500</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-1.40%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>240,841</t>
+          <t>241,331</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>224,023</t>
+          <t>209,142</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>42.36</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1482,17 +1482,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>128,500</t>
+          <t>128,000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-1,500</t>
+          <t>-2,500</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>240,150</t>
+          <t>239,215</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1512,17 +1512,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15.10</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>247,230</t>
+          <t>289,244</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1537,27 +1537,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>141,000</t>
+          <t>249,000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>+3,500</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.70%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>230,743</t>
+          <t>230,239</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>163,648</t>
+          <t>92,466</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>634,685</t>
+          <t>397,166</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.06</t>
+          <t>-51.58</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>-13.58</t>
         </is>
       </c>
     </row>
@@ -1602,27 +1602,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>237,000</t>
+          <t>139,500</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-4.44%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1632,32 +1632,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>219,143</t>
+          <t>228,289</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>92,466</t>
+          <t>163,648</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>907,510</t>
+          <t>577,803</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-49.10</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-13.58</t>
+          <t>13.23</t>
         </is>
       </c>
     </row>
@@ -1677,17 +1677,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>302,000</t>
+          <t>308,500</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-1,500</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>217,622</t>
+          <t>222,306</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>122,118</t>
+          <t>176,131</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52,100</t>
+          <t>53,000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-600</t>
+          <t>+1,500</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+2.91%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>216,636</t>
+          <t>220,378</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>67.54</t>
+          <t>67.51</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>974,374</t>
+          <t>1,353,903</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1797,62 +1797,62 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LG생활건강</t>
+          <t>SK바이오사이언스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>051900</t>
+          <t>302440</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1,383,000</t>
+          <t>274,500</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>+15,500</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>+5.98%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>216,000</t>
+          <t>209,992</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15,618</t>
+          <t>76,500</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19,636</t>
+          <t>1,931,561</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>29.04</t>
+          <t>133.71</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>13.25</t>
         </is>
       </c>
     </row>
@@ -1862,62 +1862,62 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SK바이오사이언스</t>
+          <t>LG생활건강</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>302440</t>
+          <t>051900</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>280,000</t>
+          <t>1,339,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>+2,000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>214,200</t>
+          <t>209,128</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>76,500</t>
+          <t>15,618</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>678,896</t>
+          <t>29,018</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>136.39</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>17.92</t>
         </is>
       </c>
     </row>
@@ -1937,17 +1937,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>38,750</t>
+          <t>39,650</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>+700</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+1.80%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>200,182</t>
+          <t>204,832</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>60.30</t>
+          <t>60.40</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>765,401</t>
+          <t>1,799,203</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>271,500</t>
+          <t>269,000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-4,500</t>
+          <t>-2,500</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>191,028</t>
+          <t>189,269</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>19.80</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>280,571</t>
+          <t>155,394</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2067,17 +2067,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>223,000</t>
+          <t>217,000</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.29%</t>
+          <t>-1.36%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>158,994</t>
+          <t>154,716</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>440,901</t>
+          <t>281,336</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>146.61</t>
+          <t>142.67</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2122,27 +2122,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>011200</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24,250</t>
+          <t>38,050</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+250</t>
+          <t>+200</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2152,32 +2152,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>155,676</t>
+          <t>154,252</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>641,964</t>
+          <t>405,392</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1,571,758</t>
+          <t>2,090,373</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>24.10</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.93</t>
         </is>
       </c>
     </row>
@@ -2187,27 +2187,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37,950</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-450</t>
+          <t>-400</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>153,846</t>
+          <t>152,787</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>405,392</t>
+          <t>641,964</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>3,034,510</t>
+          <t>3,255,854</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>2.91</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2262,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>94,800</t>
+          <t>95,200</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-900</t>
+          <t>-100</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>149,121</t>
+          <t>149,751</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2292,17 +2292,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>33.50</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>150,926</t>
+          <t>133,245</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2327,17 +2327,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>73,100</t>
+          <t>72,400</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>+600</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>146,200</t>
+          <t>144,800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2357,17 +2357,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>223,154</t>
+          <t>202,890</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2392,17 +2392,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>44,750</t>
+          <t>44,850</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-350</t>
+          <t>+550</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>+1.24%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>134,358</t>
+          <t>134,659</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2422,17 +2422,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>68.15</t>
+          <t>68.09</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>731,277</t>
+          <t>837,767</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>179,500</t>
+          <t>178,500</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-4,500</t>
+          <t>+1,500</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>134,075</t>
+          <t>133,328</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2487,17 +2487,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>408,187</t>
+          <t>267,885</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>589,000</t>
+          <t>596,000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>+12,000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>129,309</t>
+          <t>130,846</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>155,255</t>
+          <t>189,871</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.99</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2587,17 +2587,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>167,000</t>
+          <t>164,000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-2,500</t>
+          <t>-1,500</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>129,221</t>
+          <t>126,900</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>94,015</t>
+          <t>118,973</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>162,000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>+1,500</t>
+          <t>+4,000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>126,265</t>
+          <t>125,490</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2682,17 +2682,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>892,764</t>
+          <t>714,402</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>117.77</t>
+          <t>117.05</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2707,62 +2707,62 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>101,500</t>
+          <t>34,250</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>+500</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2,500</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>114,272</t>
+          <t>119,129</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>112,583</t>
+          <t>347,821</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.11</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>450,108</t>
+          <t>3,853,536</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-13.07</t>
+          <t>-7.22</t>
         </is>
       </c>
     </row>
@@ -2772,62 +2772,62 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>두산중공업</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21,850</t>
+          <t>105,000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>+800</t>
+          <t>+1,000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>112,747</t>
+          <t>118,212</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>516,006</t>
+          <t>112,583</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>78.12</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7,471,780</t>
+          <t>311,307</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-51.90</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-37.20</t>
+          <t>-13.07</t>
         </is>
       </c>
     </row>
@@ -2837,62 +2837,62 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>033780</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>191,000</t>
+          <t>81,100</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>+200</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>111,656</t>
+          <t>111,344</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>58,458</t>
+          <t>137,292</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>251,202</t>
+          <t>194,442</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>88.63</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>13.22</t>
         </is>
       </c>
     </row>
@@ -2902,62 +2902,62 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>32,100</t>
+          <t>228,500</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-450</t>
+          <t>+1,000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>111,650</t>
+          <t>108,252</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>347,821</t>
+          <t>47,375</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>48.81</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2,077,302</t>
+          <t>56,983</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>4.96</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>033780</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>81,300</t>
+          <t>184,500</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-100</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>111,619</t>
+          <t>107,919</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>137,292</t>
+          <t>58,493</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>37.17</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>398,171</t>
+          <t>240,987</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>85.61</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>13.22</t>
+          <t>0.78</t>
         </is>
       </c>
     </row>
@@ -3032,62 +3032,62 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>두산중공업</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>034020</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>276,500</t>
+          <t>20,550</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-550</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.07%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>107,976</t>
+          <t>106,156</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>39,051</t>
+          <t>516,572</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>112,849</t>
+          <t>4,197,079</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>98.36</t>
+          <t>-48.81</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>-37.20</t>
         </is>
       </c>
     </row>
@@ -3097,27 +3097,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>227,000</t>
+          <t>268,000</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>-2,500</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3127,32 +3127,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>107,541</t>
+          <t>104,656</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>47,375</t>
+          <t>39,051</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>16.49</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>114,575</t>
+          <t>119,763</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>95.34</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>12.52</t>
         </is>
       </c>
     </row>
@@ -3172,17 +3172,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>122,000</t>
+          <t>120,000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>104,863</t>
+          <t>103,144</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3202,17 +3202,17 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>96,200</t>
+          <t>112,682</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3237,17 +3237,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>524,000</t>
+          <t>512,000</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>+5,000</t>
+          <t>+2,000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>98,879</t>
+          <t>96,614</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3267,17 +3267,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>19.87</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>44,901</t>
+          <t>36,563</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3292,27 +3292,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>롯데케미칼</t>
+          <t>현대중공업</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>011170</t>
+          <t>329180</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>265,500</t>
+          <t>99,200</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>+11,500</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3322,32 +3322,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>91,001</t>
+          <t>88,063</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>34,275</t>
+          <t>88,773</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>376,437</t>
+          <t>2,221,113</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>-8.96</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-7.86</t>
         </is>
       </c>
     </row>
@@ -3357,62 +3357,62 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>롯데케미칼</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>011170</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>256,000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>+1,000</t>
+          <t>-2,500</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>89,277</t>
+          <t>87,745</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>78,313</t>
+          <t>34,275</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>103,771</t>
+          <t>138,028</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-150.79</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-135.18</t>
+          <t>1.22</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>16,050</t>
+          <t>16,200</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>85,675</t>
+          <t>86,476</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>18.13</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>670,565</t>
+          <t>685,134</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>32,500</t>
+          <t>32,450</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>84,861</t>
+          <t>84,731</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.20</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>609,514</t>
+          <t>549,851</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3552,62 +3552,62 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>한국조선해양</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>118,500</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>+1,000</t>
+          <t>-2,500</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>83,866</t>
+          <t>83,795</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70,773</t>
+          <t>78,313</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>319,153</t>
+          <t>219,894</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-141.53</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>-7.42</t>
+          <t>-135.18</t>
         </is>
       </c>
     </row>
@@ -3617,27 +3617,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>42,200</t>
+          <t>11,150</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-350</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3647,32 +3647,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>80,720</t>
+          <t>81,179</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>191,278</t>
+          <t>728,061</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>977,629</t>
+          <t>2,654,434</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.87</t>
         </is>
       </c>
     </row>
@@ -3682,27 +3682,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>40,750</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>-1,350</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3712,32 +3712,32 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>80,087</t>
+          <t>77,946</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>728,061</t>
+          <t>191,278</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>28.31</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2,799,370</t>
+          <t>1,116,322</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.30</t>
         </is>
       </c>
     </row>
